--- a/data/trans_camb/POLIPATOLOGIA_5-Clase-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -1,06</t>
+          <t>-4,48; -1,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,76</t>
+          <t>-1,39; 3,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,62</t>
+          <t>0,61; 5,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,58</t>
+          <t>-3,83; 3,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,01</t>
+          <t>-3,36; 3,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,58</t>
+          <t>1,18; 7,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,26</t>
+          <t>-3,36; 0,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,65</t>
+          <t>-1,41; 2,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,99</t>
+          <t>2,0; 5,87</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -39,15</t>
+          <t>-100,0; -9,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 235,53</t>
+          <t>-42,26; 220,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 349,46</t>
+          <t>7,52; 343,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 128,44</t>
+          <t>-63,72; 104,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,91; 107,23</t>
+          <t>-55,92; 117,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 267,44</t>
+          <t>12,46; 247,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,5; 17,39</t>
+          <t>-73,76; 9,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 109,28</t>
+          <t>-31,4; 108,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,71; 244,57</t>
+          <t>42,42; 232,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,67</t>
+          <t>-2,3; 1,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,17</t>
+          <t>-2,77; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,45</t>
+          <t>2,31; 7,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,23</t>
+          <t>-1,74; 4,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,51</t>
+          <t>-2,42; 3,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,82</t>
+          <t>4,94; 11,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,07</t>
+          <t>-1,63; 2,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,51</t>
+          <t>-2,08; 1,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 8,41</t>
+          <t>4,25; 8,51</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-71,07; 155,54</t>
+          <t>-68,85; 134,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,35; 118,3</t>
+          <t>-85,99; 95,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,66; 609,77</t>
+          <t>56,25; 513,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 173,71</t>
+          <t>-36,34; 173,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,77; 133,74</t>
+          <t>-49,46; 157,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,54; 514,88</t>
+          <t>81,94; 509,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 96,88</t>
+          <t>-42,95; 105,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,33; 74,11</t>
+          <t>-52,18; 74,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,25; 381,3</t>
+          <t>92,4; 389,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,21</t>
+          <t>-0,76; 3,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,67</t>
+          <t>-2,78; 1,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 8,55</t>
+          <t>-1,12; 8,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 3,05</t>
+          <t>-7,71; 2,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 14,15</t>
+          <t>-0,92; 13,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 18,34</t>
+          <t>5,38; 18,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,07</t>
+          <t>-1,58; 2,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,47</t>
+          <t>-1,32; 3,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 10,16</t>
+          <t>-1,76; 9,9</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 192,6</t>
+          <t>-21,11; 171,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,3; 76,18</t>
+          <t>-64,6; 67,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 314,32</t>
+          <t>-26,33; 308,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,74; 58,38</t>
+          <t>-63,55; 73,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 252,11</t>
+          <t>-15,72; 276,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,07; 339,03</t>
+          <t>38,7; 346,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 95,23</t>
+          <t>-27,09; 87,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 108,4</t>
+          <t>-23,05; 104,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 244,02</t>
+          <t>-27,63; 247,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,34</t>
+          <t>-0,34; 3,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,88</t>
+          <t>-2,2; 0,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,48</t>
+          <t>4,28; 8,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,28</t>
+          <t>-1,99; 3,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,82</t>
+          <t>-1,5; 3,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 57,87</t>
+          <t>5,05; 53,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,75</t>
+          <t>-0,36; 2,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,43</t>
+          <t>-1,3; 1,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 37,43</t>
+          <t>5,78; 40,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 87,38</t>
+          <t>-6,62; 92,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 24,92</t>
+          <t>-43,01; 25,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,75; 229,03</t>
+          <t>78,68; 230,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 66,27</t>
+          <t>-26,86; 68,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 83,45</t>
+          <t>-23,25; 81,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,34; 1136,22</t>
+          <t>76,19; 1235,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 62,88</t>
+          <t>-6,62; 63,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 32,45</t>
+          <t>-22,86; 35,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>105,46; 766,97</t>
+          <t>108,78; 839,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,66</t>
+          <t>-3,95; 1,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,37</t>
+          <t>-1,44; 4,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,42</t>
+          <t>1,73; 8,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,09</t>
+          <t>3,63; 10,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,2</t>
+          <t>3,54; 9,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,74; 20,51</t>
+          <t>9,98; 21,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,91</t>
+          <t>1,44; 5,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,53</t>
+          <t>2,13; 6,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,6; 14,84</t>
+          <t>8,69; 15,02</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 60,82</t>
+          <t>-60,7; 47,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 141,57</t>
+          <t>-24,74; 135,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26,5; 278,99</t>
+          <t>24,66; 268,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37,95; 198,35</t>
+          <t>43,9; 204,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>39,65; 205,37</t>
+          <t>40,2; 187,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>122,9; 386,29</t>
+          <t>128,78; 416,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,14; 123,51</t>
+          <t>19,82; 124,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,55; 135,41</t>
+          <t>27,85; 135,36</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>125,35; 307,73</t>
+          <t>125,31; 301,6</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,88</t>
+          <t>-0,31; 2,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,27</t>
+          <t>-0,61; 1,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,45</t>
+          <t>0,33; 3,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,98</t>
+          <t>2,52; 8,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,66</t>
+          <t>1,57; 6,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,83; 13,16</t>
+          <t>8,01; 13,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,53</t>
+          <t>2,4; 6,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,38</t>
+          <t>0,91; 5,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,35</t>
+          <t>5,8; 10,18</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29,74; 112,63</t>
+          <t>27,54; 112,9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19,93; 93,5</t>
+          <t>17,39; 93,68</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>82,23; 187,75</t>
+          <t>82,67; 187,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,17; 108,78</t>
+          <t>31,47; 112,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12,99; 89,93</t>
+          <t>11,84; 87,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>75,93; 174,35</t>
+          <t>73,79; 172,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,29</t>
+          <t>-0,53; 1,32</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,99</t>
+          <t>-0,69; 1,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,79</t>
+          <t>2,73; 5,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,54</t>
+          <t>1,82; 4,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,54</t>
+          <t>1,74; 4,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,12; 29,35</t>
+          <t>9,09; 29,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,64</t>
+          <t>0,94; 2,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,45</t>
+          <t>0,82; 2,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,71; 17,8</t>
+          <t>6,69; 18,62</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 44,34</t>
+          <t>-14,41; 43,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 33,13</t>
+          <t>-18,79; 35,0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>75,97; 192,67</t>
+          <t>71,97; 189,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25,11; 75,36</t>
+          <t>24,93; 73,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>23,19; 74,98</t>
+          <t>23,64; 72,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>131,29; 443,42</t>
+          <t>128,4; 438,6</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,13; 55,84</t>
+          <t>17,08; 55,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>13,92; 51,2</t>
+          <t>15,53; 52,61</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>129,51; 372,1</t>
+          <t>129,28; 364,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_5-Clase-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>4,01</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -1,05</t>
+          <t>-4,38; -1,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,7</t>
+          <t>-1,39; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,52</t>
+          <t>1,0; 5,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,23</t>
+          <t>-3,62; 2,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 3,15</t>
+          <t>-3,73; 3,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,58</t>
+          <t>0,97; 7,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,17</t>
+          <t>-3,19; 0,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,73</t>
+          <t>-1,08; 2,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,87</t>
+          <t>1,84; 5,88</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117,41%</t>
+          <t>121,79%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>111,68%</t>
+          <t>114,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,11</t>
+          <t>-100,0; -35,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 220,91</t>
+          <t>-38,74; 249,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 343,84</t>
+          <t>15,32; 348,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 104,72</t>
+          <t>-58,32; 99,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,92; 117,29</t>
+          <t>-58,48; 109,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,46; 247,82</t>
+          <t>11,75; 285,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,76; 9,44</t>
+          <t>-72,52; 11,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 108,66</t>
+          <t>-26,02; 104,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,42; 232,65</t>
+          <t>38,19; 232,74</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>8,41</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>6,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,53</t>
+          <t>-2,29; 1,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,99</t>
+          <t>-2,58; 1,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,19</t>
+          <t>2,34; 7,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 4,42</t>
+          <t>-1,96; 4,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,68</t>
+          <t>-2,85; 3,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 11,83</t>
+          <t>5,2; 11,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,11</t>
+          <t>-1,56; 2,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,61</t>
+          <t>-1,99; 1,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,51</t>
+          <t>4,33; 8,57</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>211,47%</t>
+          <t>207,95%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>218,06%</t>
+          <t>219,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>208,01%</t>
+          <t>208,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 134,23</t>
+          <t>-70,54; 133,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,99; 95,3</t>
+          <t>-82,79; 85,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,25; 513,43</t>
+          <t>63,02; 597,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 173,26</t>
+          <t>-41,1; 185,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 157,02</t>
+          <t>-56,66; 137,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,94; 509,01</t>
+          <t>89,41; 534,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 105,67</t>
+          <t>-43,22; 91,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 74,82</t>
+          <t>-51,6; 80,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,4; 389,29</t>
+          <t>98,75; 425,81</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>7,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,97</t>
+          <t>11,57</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>8,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,82</t>
+          <t>-0,67; 3,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,38</t>
+          <t>-2,61; 1,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 8,78</t>
+          <t>4,45; 10,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 2,94</t>
+          <t>-8,05; 2,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 13,65</t>
+          <t>-0,42; 14,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 18,18</t>
+          <t>5,0; 18,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,84</t>
+          <t>-1,53; 3,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,64</t>
+          <t>-1,27; 3,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 9,9</t>
+          <t>5,87; 11,31</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109,96%</t>
+          <t>223,26%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>142,58%</t>
+          <t>137,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>113,46%</t>
+          <t>195,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 171,38</t>
+          <t>-19,8; 164,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 67,53</t>
+          <t>-60,21; 75,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 308,4</t>
+          <t>98,04; 495,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,55; 73,71</t>
+          <t>-66,55; 48,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 276,47</t>
+          <t>-6,58; 235,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,7; 346,55</t>
+          <t>36,48; 362,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 87,88</t>
+          <t>-27,73; 90,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 104,67</t>
+          <t>-25,99; 100,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 247,37</t>
+          <t>98,34; 335,32</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,41</t>
+          <t>5,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,26</t>
+          <t>6,02</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,39</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,37 +1335,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 8,34</t>
+          <t>4,07; 8,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,24</t>
+          <t>-1,65; 3,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,67</t>
+          <t>-1,36; 3,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 53,16</t>
+          <t>3,33; 8,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,76</t>
+          <t>-0,4; 2,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,59</t>
+          <t>-1,35; 1,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 40,55</t>
+          <t>4,34; 7,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140,17%</t>
+          <t>132,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>408,4%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>304,02%</t>
+          <t>120,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 92,55</t>
+          <t>-0,74; 99,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 25,94</t>
+          <t>-42,94; 25,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,68; 230,27</t>
+          <t>73,35; 216,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 68,08</t>
+          <t>-23,43; 72,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 81,64</t>
+          <t>-19,6; 76,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,19; 1235,58</t>
+          <t>43,89; 176,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 63,54</t>
+          <t>-7,24; 60,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 35,47</t>
+          <t>-24,14; 33,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>108,78; 839,9</t>
+          <t>73,71; 178,46</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>18,19</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>12,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,55</t>
+          <t>-3,72; 1,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,12</t>
+          <t>-1,28; 4,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,45</t>
+          <t>0,71; 6,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 10,05</t>
+          <t>3,66; 9,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,89</t>
+          <t>3,05; 9,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,98; 21,1</t>
+          <t>15,24; 21,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,98</t>
+          <t>1,62; 6,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,5</t>
+          <t>2,19; 6,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,69; 15,02</t>
+          <t>10,06; 14,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109,09%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>241,4%</t>
+          <t>269,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>205,99%</t>
+          <t>206,88%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,7; 47,68</t>
+          <t>-59,6; 56,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 135,91</t>
+          <t>-24,69; 128,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24,66; 268,32</t>
+          <t>7,98; 189,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43,9; 204,32</t>
+          <t>41,8; 192,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>40,2; 187,21</t>
+          <t>37,5; 185,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>128,78; 416,79</t>
+          <t>172,96; 409,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,82; 124,17</t>
+          <t>23,92; 127,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,85; 135,36</t>
+          <t>31,59; 133,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>125,31; 301,6</t>
+          <t>134,89; 310,89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,61</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>8,18</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,23</t>
+          <t>-0,55; 2,15</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,29</t>
+          <t>-0,62; 1,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,44</t>
+          <t>0,65; 4,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,08</t>
+          <t>2,79; 7,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,86</t>
+          <t>1,75; 6,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,01; 13,45</t>
+          <t>7,56; 12,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,68</t>
+          <t>2,26; 6,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,12</t>
+          <t>1,21; 5,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,18</t>
+          <t>5,82; 10,49</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>497,87%</t>
+          <t>725,43%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>129,16%</t>
+          <t>123,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>120,4%</t>
+          <t>122,27%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27,54; 112,9</t>
+          <t>27,63; 108,46</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17,39; 93,68</t>
+          <t>18,24; 98,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>82,67; 187,59</t>
+          <t>79,41; 183,87</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,47; 112,96</t>
+          <t>31,6; 114,2</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>11,84; 87,36</t>
+          <t>15,66; 90,9</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>73,79; 172,3</t>
+          <t>74,11; 176,74</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,43</t>
+          <t>9,77</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,67</t>
+          <t>7,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,32</t>
+          <t>-0,59; 1,31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,07</t>
+          <t>-0,73; 1,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,79</t>
+          <t>3,78; 6,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,55</t>
+          <t>1,88; 4,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,54</t>
+          <t>1,78; 4,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,09; 29,48</t>
+          <t>8,34; 11,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,61</t>
+          <t>0,98; 2,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,46</t>
+          <t>0,83; 2,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,69; 18,62</t>
+          <t>6,6; 8,37</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>134,1%</t>
+          <t>146,28%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>215,14%</t>
+          <t>145,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>190,01%</t>
+          <t>146,77%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 43,53</t>
+          <t>-15,15; 41,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 35,0</t>
+          <t>-18,92; 33,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>71,97; 189,8</t>
+          <t>97,16; 203,56</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24,93; 73,22</t>
+          <t>26,33; 76,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>23,64; 72,58</t>
+          <t>24,41; 73,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>128,4; 438,6</t>
+          <t>113,67; 181,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,08; 55,5</t>
+          <t>17,83; 56,84</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15,53; 52,61</t>
+          <t>14,26; 50,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>129,28; 364,18</t>
+          <t>118,96; 178,04</t>
         </is>
       </c>
     </row>
